--- a/templates/GN_CoNgay.xlsx
+++ b/templates/GN_CoNgay.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t xml:space="preserve">To: </t>
   </si>
@@ -133,6 +133,12 @@
   </si>
   <si>
     <t>Phí vận chuyển, lắp đặt, tháo dỡ</t>
+  </si>
+  <si>
+    <t>VAT (8%)</t>
+  </si>
+  <si>
+    <t>Tổng Cộng</t>
   </si>
 </sst>
 </file>
@@ -1485,7 +1491,7 @@
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="45"/>
+      <c r="E22" s="1"/>
       <c r="F22" s="45"/>
       <c r="G22" s="46"/>
       <c r="H22" s="47">
@@ -1496,26 +1502,27 @@
       <c r="J22" s="48"/>
       <c r="L22" s="49"/>
     </row>
-    <row r="23" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="28"/>
       <c r="B23" s="50"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
+      <c r="F23" s="51" t="s">
+        <v>31</v>
+      </c>
       <c r="G23" s="52"/>
       <c r="H23" s="53">
         <f>H22*8%</f>
         <v>1188000</v>
       </c>
-      <c r="I23" s="2"/>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:12" s="54" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="55" t="s">
+        <v>32</v>
+      </c>
       <c r="G24" s="56"/>
       <c r="H24" s="57">
         <f>H22+H23</f>
